--- a/outputs/tabel/tabel_14_uji_kestabilan_model_terhadap_lima_seed.xlsx
+++ b/outputs/tabel/tabel_14_uji_kestabilan_model_terhadap_lima_seed.xlsx
@@ -491,7 +491,7 @@
         <v>49.11504424778761</v>
       </c>
       <c r="I2" t="n">
-        <v>78.907693741</v>
+        <v>146.5761897820003</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>48.23008849557522</v>
       </c>
       <c r="I3" t="n">
-        <v>77.30324119700072</v>
+        <v>149.6606067590001</v>
       </c>
     </row>
     <row r="4">
@@ -553,7 +553,7 @@
         <v>48.23008849557522</v>
       </c>
       <c r="I4" t="n">
-        <v>77.04857904900018</v>
+        <v>132.0713281019998</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         <v>48.23008849557522</v>
       </c>
       <c r="I5" t="n">
-        <v>77.85989454199989</v>
+        <v>130.9309504129997</v>
       </c>
     </row>
     <row r="6">
@@ -615,7 +615,7 @@
         <v>48.23008849557522</v>
       </c>
       <c r="I6" t="n">
-        <v>75.287126962</v>
+        <v>141.1541988379995</v>
       </c>
     </row>
     <row r="7">
@@ -646,7 +646,7 @@
         <v>51.32743362831859</v>
       </c>
       <c r="I7" t="n">
-        <v>83.58946835000006</v>
+        <v>141.2445426089989</v>
       </c>
     </row>
     <row r="8">
@@ -677,7 +677,7 @@
         <v>44.69026548672566</v>
       </c>
       <c r="I8" t="n">
-        <v>82.48223941599917</v>
+        <v>139.8544052829984</v>
       </c>
     </row>
     <row r="9">
@@ -708,7 +708,7 @@
         <v>47.34513274336283</v>
       </c>
       <c r="I9" t="n">
-        <v>81.93985414100007</v>
+        <v>141.1495987879989</v>
       </c>
     </row>
     <row r="10">
@@ -739,7 +739,7 @@
         <v>48.23008849557522</v>
       </c>
       <c r="I10" t="n">
-        <v>82.0299386910001</v>
+        <v>143.2858519469992</v>
       </c>
     </row>
     <row r="11">
@@ -770,7 +770,7 @@
         <v>48.23008849557522</v>
       </c>
       <c r="I11" t="n">
-        <v>81.20699594899997</v>
+        <v>146.6807433590002</v>
       </c>
     </row>
     <row r="12">
@@ -805,7 +805,7 @@
         <v>47.9646017699115</v>
       </c>
       <c r="I12" t="n">
-        <v>82.24969930939987</v>
+        <v>142.4430283971991</v>
       </c>
     </row>
     <row r="13">
@@ -840,7 +840,7 @@
         <v>48.40707964601769</v>
       </c>
       <c r="I13" t="n">
-        <v>77.28130709820016</v>
+        <v>140.0786547787999</v>
       </c>
     </row>
   </sheetData>
